--- a/saidas/metricas_resumo/valor/5_b_top_5/parte_1_historico_completo.xlsx
+++ b/saidas/metricas_resumo/valor/5_b_top_5/parte_1_historico_completo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Modelo</t>
   </si>
@@ -49,52 +49,34 @@
     <t>SARIMA</t>
   </si>
   <si>
-    <t>ExtraTrees(EXT,j90)</t>
-  </si>
-  <si>
-    <t>POLY+ABR</t>
+    <t>VotingRegressor (RandomForest + ExtraTrees + XGBoost)</t>
   </si>
   <si>
     <t>Pipeline Antiga em Producao</t>
   </si>
   <si>
-    <t>Voting(GBR+XGB+RFR)</t>
-  </si>
-  <si>
-    <t>89/209</t>
-  </si>
-  <si>
-    <t>92/209</t>
-  </si>
-  <si>
-    <t>75/209</t>
-  </si>
-  <si>
-    <t>97/211</t>
-  </si>
-  <si>
-    <t>85/209</t>
-  </si>
-  <si>
-    <t>158/209</t>
-  </si>
-  <si>
-    <t>164/209</t>
-  </si>
-  <si>
-    <t>144/209</t>
-  </si>
-  <si>
-    <t>156/211</t>
-  </si>
-  <si>
-    <t>146/209</t>
-  </si>
-  <si>
-    <t>209/209</t>
-  </si>
-  <si>
-    <t>211/211</t>
+    <t>112/259</t>
+  </si>
+  <si>
+    <t>104/259</t>
+  </si>
+  <si>
+    <t>94/260</t>
+  </si>
+  <si>
+    <t>193/259</t>
+  </si>
+  <si>
+    <t>181/259</t>
+  </si>
+  <si>
+    <t>168/260</t>
+  </si>
+  <si>
+    <t>259/259</t>
+  </si>
+  <si>
+    <t>260/260</t>
   </si>
 </sst>
 </file>
@@ -452,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -492,31 +474,31 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>7.17</v>
+        <v>7.31</v>
       </c>
       <c r="C2">
-        <v>9.279999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="D2">
-        <v>0.756</v>
+        <v>0.753</v>
       </c>
       <c r="E2">
-        <v>-6316.9</v>
+        <v>31445.1</v>
       </c>
       <c r="F2">
-        <v>427119.7</v>
+        <v>439670.9</v>
       </c>
       <c r="G2">
-        <v>30.27</v>
+        <v>39.85</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -524,31 +506,31 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>7.2</v>
+        <v>8.19</v>
       </c>
       <c r="C3">
-        <v>9.609999999999999</v>
+        <v>10.77</v>
       </c>
       <c r="D3">
-        <v>0.72</v>
+        <v>0.673</v>
       </c>
       <c r="E3">
-        <v>79400.8</v>
+        <v>147360.4</v>
       </c>
       <c r="F3">
-        <v>450801</v>
+        <v>485195.7</v>
       </c>
       <c r="G3">
-        <v>42.56</v>
+        <v>35.51</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -556,95 +538,31 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>8.119999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="C4">
-        <v>10.33</v>
+        <v>10.75</v>
       </c>
       <c r="D4">
-        <v>0.6840000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="E4">
-        <v>113974.9</v>
+        <v>46273.5</v>
       </c>
       <c r="F4">
-        <v>472644.7</v>
+        <v>486650.6</v>
       </c>
       <c r="G4">
-        <v>32.44</v>
+        <v>41.02</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>7.19</v>
-      </c>
-      <c r="C5">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="D5">
-        <v>0.748</v>
-      </c>
-      <c r="E5">
-        <v>29980.4</v>
-      </c>
-      <c r="F5">
-        <v>433778.4</v>
-      </c>
-      <c r="G5">
-        <v>39.52</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>7.97</v>
-      </c>
-      <c r="C6">
-        <v>10.65</v>
-      </c>
-      <c r="D6">
-        <v>0.66</v>
-      </c>
-      <c r="E6">
-        <v>134676.1</v>
-      </c>
-      <c r="F6">
-        <v>485427.5</v>
-      </c>
-      <c r="G6">
-        <v>33.35</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
